--- a/jpcore-r4/feature/fix-tx-error/ValueSet-jp-condition-disease-code-icd10-vs.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/ValueSet-jp-condition-disease-code-icd10-vs.xlsx
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ConditionDiseaseCodeICD10_CS</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/ICD10-2013-full</t>
   </si>
 </sst>
 </file>
